--- a/hours _log.xlsx
+++ b/hours _log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\grant_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEB53B1B-17C4-484C-8010-D59B697814F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B3155C-2609-45E5-B975-271A70A4A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" xr2:uid="{5C0BC161-4DC7-4EE5-9C4C-8AE059B38DA9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C0BC161-4DC7-4EE5-9C4C-8AE059B38DA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -426,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E561651-AFD3-4A1E-BE8A-2464F14EF1F9}">
-  <dimension ref="F3:H6"/>
+  <dimension ref="F3:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -474,6 +474,22 @@
         <v>3</v>
       </c>
     </row>
+    <row r="7" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1">
+        <v>46256</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1">
+        <v>46257</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
